--- a/data/trans_camb/IP04D$aparatos-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Habitat-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,76; -8,45</t>
+          <t>-29,68; -10,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 4,3</t>
+          <t>-14,87; 4,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,37; -0,3</t>
+          <t>-19,33; 0,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 5,62</t>
+          <t>-23,58; 5,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,71; -7,09</t>
+          <t>-21,76; -8,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 1,75</t>
+          <t>-16,55; 1,23</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,84; -13,08</t>
+          <t>-39,2; -14,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 6,77</t>
+          <t>-20,04; 6,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,76; -0,43</t>
+          <t>-27,4; -0,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 8,6</t>
+          <t>-32,24; 8,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,16; -10,95</t>
+          <t>-30,4; -12,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,14; 2,62</t>
+          <t>-23,64; 1,79</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,69; -1,18</t>
+          <t>-16,91; -1,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 6,08</t>
+          <t>-11,06; 6,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,47; -5,07</t>
+          <t>-19,8; -5,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 5,65</t>
+          <t>-10,0; 5,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,1; -5,59</t>
+          <t>-16,37; -5,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 3,9</t>
+          <t>-7,88; 3,61</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,18; -2,4</t>
+          <t>-25,73; -2,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 10,39</t>
+          <t>-16,57; 10,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,53; -8,22</t>
+          <t>-28,68; -8,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 8,97</t>
+          <t>-14,28; 8,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,1; -9,22</t>
+          <t>-24,13; -8,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 6,24</t>
+          <t>-11,76; 5,85</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,61; -16,88</t>
+          <t>-34,42; -17,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 11,82</t>
+          <t>-11,38; 12,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-33,14; -15,73</t>
+          <t>-33,18; -15,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,49; -0,53</t>
+          <t>-19,16; -0,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,58; -18,39</t>
+          <t>-31,07; -18,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 3,77</t>
+          <t>-12,1; 4,47</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,2; -25,04</t>
+          <t>-46,15; -25,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 17,95</t>
+          <t>-15,54; 18,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,11; -24,66</t>
+          <t>-47,13; -25,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,5; -0,54</t>
+          <t>-27,11; -0,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,0; -27,83</t>
+          <t>-43,59; -28,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 5,57</t>
+          <t>-17,25; 7,0</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 6,57</t>
+          <t>-9,53; 6,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 6,85</t>
+          <t>-10,34; 7,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 15,67</t>
+          <t>-0,62; 15,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 9,21</t>
+          <t>-7,96; 9,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 8,49</t>
+          <t>-3,85; 8,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 5,04</t>
+          <t>-6,47; 6,17</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 12,87</t>
+          <t>-15,87; 13,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 13,25</t>
+          <t>-17,56; 13,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 35,42</t>
+          <t>-1,3; 33,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 19,48</t>
+          <t>-15,1; 20,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 17,04</t>
+          <t>-7,18; 16,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 9,99</t>
+          <t>-11,95; 12,32</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -7,9</t>
+          <t>-16,5; -7,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 4,09</t>
+          <t>-6,65; 4,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,06; -4,8</t>
+          <t>-13,46; -5,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 1,46</t>
+          <t>-8,36; 1,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -7,73</t>
+          <t>-13,89; -7,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 0,87</t>
+          <t>-6,69; 0,75</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -12,66</t>
+          <t>-24,84; -12,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 6,5</t>
+          <t>-10,04; 7,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -8,01</t>
+          <t>-21,1; -8,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 2,47</t>
+          <t>-13,15; 1,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,54; -12,49</t>
+          <t>-21,77; -12,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 1,42</t>
+          <t>-10,34; 1,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$aparatos-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Habitat-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,68; -10,51</t>
+          <t>-28,72; -8,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 4,25</t>
+          <t>-15,46; 4,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 0,08</t>
+          <t>-19,68; 0,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 5,43</t>
+          <t>-21,58; 6,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,76; -8,16</t>
+          <t>-21,83; -8,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 1,23</t>
+          <t>-17,34; 1,4</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,2; -14,82</t>
+          <t>-38,27; -13,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 6,05</t>
+          <t>-20,36; 6,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,4; -0,04</t>
+          <t>-28,38; 0,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 8,66</t>
+          <t>-31,91; 9,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,4; -12,41</t>
+          <t>-30,92; -12,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 1,79</t>
+          <t>-24,27; 2,24</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,91; -1,27</t>
+          <t>-16,23; -2,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 6,4</t>
+          <t>-11,5; 5,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,8; -5,11</t>
+          <t>-20,58; -5,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 5,27</t>
+          <t>-9,08; 5,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -5,33</t>
+          <t>-16,61; -5,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 3,61</t>
+          <t>-7,78; 3,66</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,73; -2,21</t>
+          <t>-24,52; -3,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 10,55</t>
+          <t>-17,22; 8,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,68; -8,07</t>
+          <t>-29,25; -7,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 8,35</t>
+          <t>-13,36; 9,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,13; -8,6</t>
+          <t>-24,47; -9,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 5,85</t>
+          <t>-11,47; 5,93</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-34,42; -17,07</t>
+          <t>-33,31; -15,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 12,52</t>
+          <t>-11,42; 11,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-33,18; -15,88</t>
+          <t>-31,97; -15,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -0,26</t>
+          <t>-18,84; -0,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,07; -18,72</t>
+          <t>-30,58; -18,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 4,47</t>
+          <t>-12,35; 4,01</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,15; -25,58</t>
+          <t>-45,19; -24,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 18,83</t>
+          <t>-15,74; 17,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,13; -25,59</t>
+          <t>-45,32; -24,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,11; -0,29</t>
+          <t>-26,7; -0,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,59; -28,03</t>
+          <t>-43,43; -27,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 7,0</t>
+          <t>-17,08; 6,02</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 6,74</t>
+          <t>-9,75; 6,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 7,03</t>
+          <t>-9,74; 7,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 15,1</t>
+          <t>-2,31; 14,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 9,6</t>
+          <t>-8,45; 9,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 8,32</t>
+          <t>-2,39; 8,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 6,17</t>
+          <t>-7,41; 5,02</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 13,28</t>
+          <t>-16,56; 12,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 13,3</t>
+          <t>-16,03; 15,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 33,24</t>
+          <t>-4,33; 31,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 20,46</t>
+          <t>-15,54; 20,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 16,37</t>
+          <t>-4,47; 16,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 12,32</t>
+          <t>-12,9; 10,17</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -7,96</t>
+          <t>-16,94; -8,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 4,3</t>
+          <t>-6,69; 4,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,46; -5,19</t>
+          <t>-13,31; -5,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 1,36</t>
+          <t>-8,57; 1,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,89; -7,73</t>
+          <t>-13,77; -7,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 0,75</t>
+          <t>-5,76; 1,24</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,84; -12,81</t>
+          <t>-25,55; -12,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 7,01</t>
+          <t>-10,29; 6,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -8,56</t>
+          <t>-20,81; -8,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 1,95</t>
+          <t>-13,79; 2,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,77; -12,72</t>
+          <t>-21,45; -12,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 1,25</t>
+          <t>-9,08; 1,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$aparatos-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Habitat-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-10,12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-19,58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-5,65</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-10,12</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,47</t>
+          <t>-4,78</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,2</t>
+          <t>-3,88</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,72; -8,65</t>
+          <t>-19,37; -0,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 4,24</t>
+          <t>-17,38; 8,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 0,32</t>
+          <t>-28,76; -8,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 6,26</t>
+          <t>-14,22; 5,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,83; -8,12</t>
+          <t>-20,71; -7,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 1,4</t>
+          <t>-12,54; 3,58</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-15,39%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-4,89%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-27,33%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-7,88%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-15,39%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-9,84%</t>
+          <t>-6,68%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-9,04%</t>
+          <t>-5,66%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,27; -13,34</t>
+          <t>-27,76; -0,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 6,32</t>
+          <t>-24,99; 12,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 0,44</t>
+          <t>-38,84; -13,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 9,81</t>
+          <t>-18,61; 7,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,92; -12,13</t>
+          <t>-29,16; -10,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 2,24</t>
+          <t>-17,88; 5,29</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-12,07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-9,27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,98</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-12,07</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,92</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,79</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,23; -2,18</t>
+          <t>-19,47; -5,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 5,24</t>
+          <t>-7,8; 7,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,58; -5,14</t>
+          <t>-16,69; -1,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 5,95</t>
+          <t>-8,12; 7,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,61; -5,73</t>
+          <t>-16,1; -5,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 3,66</t>
+          <t>-5,45; 5,63</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-18,17%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-0,22%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-14,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,11%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-18,17%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,88%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,75%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,52; -3,77</t>
+          <t>-28,53; -8,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 8,48</t>
+          <t>-11,21; 11,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,25; -7,47</t>
+          <t>-25,18; -2,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 9,69</t>
+          <t>-12,02; 13,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,47; -9,1</t>
+          <t>-24,1; -9,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 5,93</t>
+          <t>-8,03; 8,94</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-24,16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-8,27</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-25,45</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-24,16</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-9,29</t>
+          <t>-4,3</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,22</t>
+          <t>-6,36</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,31; -15,47</t>
+          <t>-33,14; -15,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 11,87</t>
+          <t>-18,59; 1,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-31,97; -15,72</t>
+          <t>-33,61; -16,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,84; -0,48</t>
+          <t>-12,36; 5,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,58; -18,2</t>
+          <t>-30,58; -18,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 4,01</t>
+          <t>-12,86; 0,27</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-36,22%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-12,4%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-35,93%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-2,04%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-36,22%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-13,93%</t>
+          <t>-6,07%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-7,6%</t>
+          <t>-9,26%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -24,17</t>
+          <t>-47,11; -24,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 17,67</t>
+          <t>-26,25; 1,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-45,32; -24,84</t>
+          <t>-45,2; -25,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,7; -0,5</t>
+          <t>-16,53; 7,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,43; -27,41</t>
+          <t>-43,0; -27,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 6,02</t>
+          <t>-18,24; 0,36</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,09</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-1,73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,09</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,49</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 6,5</t>
+          <t>-0,55; 15,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 7,98</t>
+          <t>-8,24; 9,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 14,42</t>
+          <t>-9,78; 6,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 9,49</t>
+          <t>-10,72; 7,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 8,33</t>
+          <t>-3,11; 8,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 5,02</t>
+          <t>-7,86; 5,35</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-3,11%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-3,91%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14,12%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>-3,48%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-1,38%</t>
+          <t>-0,92%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 12,39</t>
+          <t>-1,04; 35,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 15,75</t>
+          <t>-15,43; 19,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 31,02</t>
+          <t>-16,97; 12,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 20,5</t>
+          <t>-18,26; 13,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 16,71</t>
+          <t>-5,48; 17,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 10,17</t>
+          <t>-13,95; 10,59</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-9,09</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,77</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-12,62</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-1,85</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-9,09</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,24</t>
+          <t>-1,98</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>-1,9</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -8,03</t>
+          <t>-13,06; -4,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 4,45</t>
+          <t>-6,6; 2,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,31; -5,0</t>
+          <t>-16,72; -7,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 1,5</t>
+          <t>-6,42; 2,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,77; -7,92</t>
+          <t>-13,92; -7,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 1,24</t>
+          <t>-5,06; 1,36</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-14,69%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-2,87%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-19,61%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-2,87%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-14,69%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>-3,07%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-4,18%</t>
+          <t>-3,01%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,55; -12,95</t>
+          <t>-20,56; -8,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 6,93</t>
+          <t>-10,35; 4,63</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -8,27</t>
+          <t>-25,27; -12,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 2,36</t>
+          <t>-9,59; 3,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,45; -12,79</t>
+          <t>-21,54; -12,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 1,99</t>
+          <t>-7,92; 2,21</t>
         </is>
       </c>
     </row>
